--- a/Automation/tests/New_Testcase.xlsx
+++ b/Automation/tests/New_Testcase.xlsx
@@ -130,10 +130,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -165,10 +165,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -407,8 +407,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J97"/>
+  <cols>
+    <col min="2" max="2" customWidth="1" width="74.875"/>
+    <col min="3" max="3" customWidth="1" width="62.25"/>
+    <col min="4" max="4" customWidth="1" width="20.125"/>
+    <col min="5" max="5" customWidth="1" width="9.5"/>
+    <col min="6" max="6" customWidth="1" width="19.375"/>
+    <col min="7" max="7" customWidth="1" width="22.125"/>
+    <col min="8" max="8" customWidth="1" width="20.25"/>
+    <col min="9" max="9" customWidth="1" width="26"/>
+    <col min="10" max="10" customWidth="1" width="12.5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="str">
         <v>Test case</v>
       </c>
@@ -434,13 +445,13 @@
         <v>Console Error Validated</v>
       </c>
       <c r="I1" t="str">
-        <v>Run Shakeout in Prod and POC</v>
+        <v>Run for Smoketest in POC</v>
       </c>
       <c r="J1" t="str">
         <v>Last Validated</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="str">
         <v>Scenario 1</v>
       </c>
@@ -448,7 +459,7 @@
         <v>Authentication Flow</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" t="str">
         <v>TC-1</v>
       </c>
@@ -465,7 +476,7 @@
         <v>Yes</v>
       </c>
       <c r="G3" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="H3" t="str">
         <v>Yes</v>
@@ -477,7 +488,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" t="str">
         <v>TC-2</v>
       </c>
@@ -497,7 +508,7 @@
         <v>Yes</v>
       </c>
       <c r="G4" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="H4" t="str">
         <v>Yes</v>
@@ -509,7 +520,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" t="str">
         <v>TC-3</v>
       </c>
@@ -529,7 +540,7 @@
         <v>Yes</v>
       </c>
       <c r="G5" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="H5" t="str">
         <v>Yes</v>
@@ -541,7 +552,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" t="str">
         <v>Scenario 2</v>
       </c>
@@ -552,7 +563,7 @@
         <v>TG-2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" t="str">
         <v>TC-1</v>
       </c>
@@ -581,7 +592,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" t="str">
         <v>TC-2</v>
       </c>
@@ -610,7 +621,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" t="str">
         <v>TC-3</v>
       </c>
@@ -627,7 +638,7 @@
         <v>Yes</v>
       </c>
       <c r="G9" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="H9" t="str">
         <v>Yes</v>
@@ -639,7 +650,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" t="str">
         <v>TC-4</v>
       </c>
@@ -656,7 +667,7 @@
         <v>Yes</v>
       </c>
       <c r="G10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="H10" t="str">
         <v>Yes</v>
@@ -668,7 +679,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" t="str">
         <v>TC-5</v>
       </c>
@@ -697,7 +708,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" t="str">
         <v>TC-6</v>
       </c>
@@ -714,7 +725,7 @@
         <v>Yes</v>
       </c>
       <c r="G12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="H12" t="str">
         <v>Yes</v>
@@ -726,7 +737,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" t="str">
         <v>Scenario 3</v>
       </c>
@@ -737,7 +748,7 @@
         <v>TG-3</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" t="str">
         <v>TC-1</v>
       </c>
@@ -754,7 +765,7 @@
         <v>Yes</v>
       </c>
       <c r="G14" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="H14" t="str">
         <v>No</v>
@@ -766,7 +777,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" t="str">
         <v>TC-2</v>
       </c>
@@ -780,7 +791,7 @@
         <v>Yes</v>
       </c>
       <c r="G15" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="H15" t="str">
         <v>No</v>
@@ -792,7 +803,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" t="str">
         <v>TC-3</v>
       </c>
@@ -806,7 +817,7 @@
         <v>Yes</v>
       </c>
       <c r="G16" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="H16" t="str">
         <v>No</v>
@@ -818,7 +829,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" t="str">
         <v>TC-4</v>
       </c>
@@ -832,7 +843,7 @@
         <v>Yes</v>
       </c>
       <c r="G17" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="H17" t="str">
         <v>No</v>
@@ -844,7 +855,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" t="str">
         <v>TC-5</v>
       </c>
@@ -858,7 +869,7 @@
         <v>Yes</v>
       </c>
       <c r="G18" t="str">
-        <v>yes</v>
+        <v>No</v>
       </c>
       <c r="H18" t="str">
         <v>No</v>
@@ -870,7 +881,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" t="str">
         <v>TC-6</v>
       </c>
@@ -884,7 +895,7 @@
         <v>Yes</v>
       </c>
       <c r="G19" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="H19" t="str">
         <v>No</v>
@@ -893,7 +904,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" t="str">
         <v>TC-7</v>
       </c>
@@ -916,7 +927,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" t="str">
         <v>Scenario 4</v>
       </c>
@@ -924,7 +935,7 @@
         <v>Navigation - Admin Tab - Login with Admin User</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" t="str">
         <v>TC-1</v>
       </c>
@@ -953,7 +964,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" t="str">
         <v>TC-2</v>
       </c>
@@ -982,7 +993,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" t="str">
         <v>TC-3</v>
       </c>
@@ -1008,7 +1019,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" t="str">
         <v>TC-4</v>
       </c>
@@ -1037,7 +1048,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" t="str">
         <v>TC-5</v>
       </c>
@@ -1063,7 +1074,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" t="str">
         <v>TC-6</v>
       </c>
@@ -1089,7 +1100,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" t="str">
         <v>Scenario 5</v>
       </c>
@@ -1097,7 +1108,7 @@
         <v>Audit Lifecycle - Create new Audit</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" t="str">
         <v>TC-1</v>
       </c>
@@ -1120,13 +1131,13 @@
         <v>Yes</v>
       </c>
       <c r="I29" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J29" t="str">
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" t="str">
         <v>TC-2</v>
       </c>
@@ -1149,13 +1160,13 @@
         <v>Yes</v>
       </c>
       <c r="I30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J30" t="str">
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" t="str">
         <v>TC-3</v>
       </c>
@@ -1178,13 +1189,13 @@
         <v>Yes</v>
       </c>
       <c r="I31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J31" t="str">
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" t="str">
         <v>TC-4</v>
       </c>
@@ -1207,13 +1218,13 @@
         <v>Yes</v>
       </c>
       <c r="I32" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J32" t="str">
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" t="str">
         <v>TC-5</v>
       </c>
@@ -1233,13 +1244,13 @@
         <v>Yes</v>
       </c>
       <c r="I33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J33" t="str">
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" t="str">
         <v>TC-6</v>
       </c>
@@ -1259,13 +1270,13 @@
         <v>Yes</v>
       </c>
       <c r="I34" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J34" t="str">
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" t="str">
         <v>TC-7</v>
       </c>
@@ -1285,13 +1296,13 @@
         <v>Yes</v>
       </c>
       <c r="I35" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J35" t="str">
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" t="str">
         <v>TC-8</v>
       </c>
@@ -1314,13 +1325,13 @@
         <v>Yes</v>
       </c>
       <c r="I36" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J36" t="str">
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" t="str">
         <v>TC-9</v>
       </c>
@@ -1340,13 +1351,13 @@
         <v>Yes</v>
       </c>
       <c r="I37" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J37" t="str">
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" t="str">
         <v>TC-10</v>
       </c>
@@ -1372,7 +1383,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" t="str">
         <v>TC-11</v>
       </c>
@@ -1401,7 +1412,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" t="str">
         <v>TC-12</v>
       </c>
@@ -1427,7 +1438,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" t="str">
         <v>TC-13</v>
       </c>
@@ -1453,7 +1464,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" t="str">
         <v>TC-14</v>
       </c>
@@ -1479,7 +1490,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" t="str">
         <v>TC-15</v>
       </c>
@@ -1505,7 +1516,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" t="str">
         <v>TC-16</v>
       </c>
@@ -1531,7 +1542,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" t="str">
         <v>TC-17</v>
       </c>
@@ -1560,7 +1571,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" t="str">
         <v>TC-18</v>
       </c>
@@ -1589,7 +1600,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" t="str">
         <v>Scenario 6</v>
       </c>
@@ -1597,7 +1608,7 @@
         <v>Audit Lifecycle - Search and Load Existing Audit</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" t="str">
         <v>TC-1</v>
       </c>
@@ -1623,7 +1634,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" t="str">
         <v>TC-2</v>
       </c>
@@ -1652,7 +1663,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" t="str">
         <v>TC-3</v>
       </c>
@@ -1681,7 +1692,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" t="str">
         <v>TC-4</v>
       </c>
@@ -1710,7 +1721,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" t="str">
         <v>TC-5</v>
       </c>
@@ -1739,7 +1750,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" t="str">
         <v>TC-6</v>
       </c>
@@ -1765,7 +1776,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" t="str">
         <v>TC-7</v>
       </c>
@@ -1791,7 +1802,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" t="str">
         <v>TC-8</v>
       </c>
@@ -1817,7 +1828,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" t="str">
         <v>TC-9</v>
       </c>
@@ -1843,7 +1854,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" t="str">
         <v>TC-10</v>
       </c>
@@ -1869,7 +1880,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" t="str">
         <v>TC-11</v>
       </c>
@@ -1895,7 +1906,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" t="str">
         <v>TC-12</v>
       </c>
@@ -1924,7 +1935,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" t="str">
         <v>TC-13</v>
       </c>
@@ -1953,7 +1964,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" t="str">
         <v>TC-14</v>
       </c>
@@ -1982,7 +1993,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" t="str">
         <v>TC-15</v>
       </c>
@@ -2008,7 +2019,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" t="str">
         <v>TC-16</v>
       </c>
@@ -2034,7 +2045,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" t="str">
         <v>TC-17</v>
       </c>
@@ -2060,7 +2071,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" t="str">
         <v>TC-18</v>
       </c>
@@ -2089,7 +2100,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" t="str">
         <v>TC-19</v>
       </c>
@@ -2118,7 +2129,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" t="str">
         <v>TC-20</v>
       </c>
@@ -2141,7 +2152,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" t="str">
         <v>TC-21</v>
       </c>
@@ -2164,7 +2175,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" t="str">
         <v>TC-22</v>
       </c>
@@ -2187,7 +2198,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" t="str">
         <v>TC-23</v>
       </c>
@@ -2210,7 +2221,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" t="str">
         <v>TC-24</v>
       </c>
@@ -2236,7 +2247,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" t="str">
         <v>TC-25</v>
       </c>
@@ -2259,7 +2270,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" t="str">
         <v>Scenario 7</v>
       </c>
@@ -2291,7 +2302,7 @@
         <v/>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" t="str">
         <v>TC-1</v>
       </c>
@@ -2311,7 +2322,7 @@
         <v>Yes</v>
       </c>
       <c r="G74" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H74" t="str">
         <v>No</v>
@@ -2323,7 +2334,7 @@
         <v/>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" t="str">
         <v>TC-2</v>
       </c>
@@ -2343,7 +2354,7 @@
         <v>Yes</v>
       </c>
       <c r="G75" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H75" t="str">
         <v>No</v>
@@ -2355,7 +2366,7 @@
         <v/>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" t="str">
         <v>TC-3</v>
       </c>
@@ -2375,7 +2386,7 @@
         <v>Yes</v>
       </c>
       <c r="G76" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H76" t="str">
         <v>No</v>
@@ -2387,7 +2398,7 @@
         <v/>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" t="str">
         <v>TC-4</v>
       </c>
@@ -2407,7 +2418,7 @@
         <v>Yes</v>
       </c>
       <c r="G77" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H77" t="str">
         <v>No</v>
@@ -2419,7 +2430,7 @@
         <v/>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" t="str">
         <v>TC-5</v>
       </c>
@@ -2439,7 +2450,7 @@
         <v>Yes</v>
       </c>
       <c r="G78" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H78" t="str">
         <v>No</v>
@@ -2451,7 +2462,7 @@
         <v/>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" t="str">
         <v>TC-6</v>
       </c>
@@ -2471,7 +2482,7 @@
         <v>Yes</v>
       </c>
       <c r="G79" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H79" t="str">
         <v>No</v>
@@ -2483,7 +2494,7 @@
         <v/>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" t="str">
         <v>TC-7</v>
       </c>
@@ -2503,7 +2514,7 @@
         <v>Yes</v>
       </c>
       <c r="G80" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H80" t="str">
         <v>No</v>
@@ -2515,7 +2526,7 @@
         <v/>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" t="str">
         <v>TC-8</v>
       </c>
@@ -2535,7 +2546,7 @@
         <v>Yes</v>
       </c>
       <c r="G81" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H81" t="str">
         <v>No</v>
@@ -2547,7 +2558,7 @@
         <v/>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" t="str">
         <v>TC-9</v>
       </c>
@@ -2567,7 +2578,7 @@
         <v>Yes</v>
       </c>
       <c r="G82" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H82" t="str">
         <v>No</v>
@@ -2579,7 +2590,7 @@
         <v/>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" t="str">
         <v>TC-10</v>
       </c>
@@ -2599,7 +2610,7 @@
         <v>Yes</v>
       </c>
       <c r="G83" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H83" t="str">
         <v>No</v>
@@ -2611,7 +2622,7 @@
         <v/>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" t="str">
         <v>TC-11</v>
       </c>
@@ -2631,7 +2642,7 @@
         <v>Yes</v>
       </c>
       <c r="G84" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H84" t="str">
         <v>No</v>
@@ -2643,7 +2654,7 @@
         <v/>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" t="str">
         <v>TC-12</v>
       </c>
@@ -2663,7 +2674,7 @@
         <v>Yes</v>
       </c>
       <c r="G85" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H85" t="str">
         <v>No</v>
@@ -2675,7 +2686,7 @@
         <v/>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" t="str">
         <v>TC-13</v>
       </c>
@@ -2695,7 +2706,7 @@
         <v>Yes</v>
       </c>
       <c r="G86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H86" t="str">
         <v>No</v>
@@ -2707,7 +2718,7 @@
         <v/>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" t="str">
         <v>TC-14</v>
       </c>
@@ -2727,7 +2738,7 @@
         <v>Yes</v>
       </c>
       <c r="G87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H87" t="str">
         <v>No</v>
@@ -2739,7 +2750,7 @@
         <v/>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" t="str">
         <v>TC-15</v>
       </c>
@@ -2759,7 +2770,7 @@
         <v>Yes</v>
       </c>
       <c r="G88" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H88" t="str">
         <v>No</v>
@@ -2771,7 +2782,7 @@
         <v/>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" t="str">
         <v>TC-16</v>
       </c>
@@ -2791,7 +2802,7 @@
         <v>Yes</v>
       </c>
       <c r="G89" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H89" t="str">
         <v>No</v>
@@ -2803,7 +2814,7 @@
         <v/>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" t="str">
         <v>TC-17</v>
       </c>
@@ -2823,7 +2834,7 @@
         <v>Yes</v>
       </c>
       <c r="G90" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H90" t="str">
         <v>No</v>
@@ -2835,7 +2846,7 @@
         <v/>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" t="str">
         <v>TC-18</v>
       </c>
@@ -2855,7 +2866,7 @@
         <v>Yes</v>
       </c>
       <c r="G91" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H91" t="str">
         <v>No</v>
@@ -2867,7 +2878,7 @@
         <v/>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" t="str">
         <v>TC-19</v>
       </c>
@@ -2887,7 +2898,7 @@
         <v>Yes</v>
       </c>
       <c r="G92" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H92" t="str">
         <v>No</v>
@@ -2899,7 +2910,7 @@
         <v/>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" t="str">
         <v>TC-19b</v>
       </c>
@@ -2919,7 +2930,7 @@
         <v>Yes</v>
       </c>
       <c r="G93" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H93" t="str">
         <v>No</v>
@@ -2931,7 +2942,7 @@
         <v/>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" t="str">
         <v>TC-20</v>
       </c>
@@ -2951,7 +2962,7 @@
         <v>Yes</v>
       </c>
       <c r="G94" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H94" t="str">
         <v>No</v>
@@ -2963,7 +2974,7 @@
         <v/>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" t="str">
         <v>TC-21</v>
       </c>
@@ -2983,7 +2994,7 @@
         <v>Yes</v>
       </c>
       <c r="G95" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H95" t="str">
         <v>No</v>
@@ -2995,7 +3006,7 @@
         <v/>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" t="str">
         <v>TC-22</v>
       </c>
@@ -3015,7 +3026,7 @@
         <v>Yes</v>
       </c>
       <c r="G96" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H96" t="str">
         <v>No</v>
@@ -3027,7 +3038,7 @@
         <v/>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" t="str">
         <v>TC-23</v>
       </c>
@@ -3047,7 +3058,7 @@
         <v>Yes</v>
       </c>
       <c r="G97" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H97" t="str">
         <v>No</v>
@@ -3071,7 +3082,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G39"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="str">
         <v>Test case</v>
       </c>
@@ -3094,7 +3105,7 @@
         <v>Identifier</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="str">
         <v>E2E Flow 1</v>
       </c>
@@ -3102,7 +3113,7 @@
         <v>Audit Lifecycle - Create new Audit</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" t="str">
         <v>TC-1</v>
       </c>
@@ -3122,7 +3133,7 @@
         <v>button[aria-label="Create new"]</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" t="str">
         <v>TC-2</v>
       </c>
@@ -3142,7 +3153,7 @@
         <v>[role="menuitem"]:has-text("Create audit")</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" t="str">
         <v>TC-3</v>
       </c>
@@ -3162,7 +3173,7 @@
         <v>[role="dialog"] button:has-text("Close")</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" t="str">
         <v>TC-4</v>
       </c>
@@ -3182,7 +3193,7 @@
         <v>button[aria-label="Create new"] (reopen)</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" t="str">
         <v>TC-5</v>
       </c>
@@ -3205,7 +3216,7 @@
         <v>[role="dialog"] button:has-text("Create audit")[disabled]</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" t="str">
         <v>TC-6</v>
       </c>
@@ -3228,7 +3239,7 @@
         <v>input#audit-name</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" t="str">
         <v>TC-7</v>
       </c>
@@ -3251,7 +3262,7 @@
         <v>[role="dialog"] button:has-text("Create audit")[disabled]</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" t="str">
         <v>TC-8</v>
       </c>
@@ -3271,7 +3282,7 @@
         <v>input[placeholder="Search frameworks..."]</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" t="str">
         <v>TC-9</v>
       </c>
@@ -3294,7 +3305,7 @@
         <v>[role="dialog"] button:has-text("Create audit")[enabled]</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" t="str">
         <v>TC-10</v>
       </c>
@@ -3317,7 +3328,7 @@
         <v>input#audit-start</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" t="str">
         <v>TC-11</v>
       </c>
@@ -3337,7 +3348,7 @@
         <v>input#audit-due</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" t="str">
         <v>TC-12</v>
       </c>
@@ -3360,7 +3371,7 @@
         <v>input[placeholder="Search users..."] → select Matrix_Admin</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" t="str">
         <v>TC-13</v>
       </c>
@@ -3383,7 +3394,7 @@
         <v>input[placeholder*="internal"] → first option</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" t="str">
         <v>TC-14</v>
       </c>
@@ -3406,7 +3417,7 @@
         <v>input[placeholder*="external"] → first option</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" t="str">
         <v>TC-15</v>
       </c>
@@ -3429,7 +3440,7 @@
         <v>(skip — leave blank)</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" t="str">
         <v>TC-16</v>
       </c>
@@ -3452,7 +3463,7 @@
         <v>textarea#audit-desc</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" t="str">
         <v>TC-17</v>
       </c>
@@ -3472,7 +3483,7 @@
         <v>[role="dialog"] button:has-text("Create audit").click()</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" t="str">
         <v>TC-18</v>
       </c>
@@ -3492,7 +3503,7 @@
         <v>a[href*="/audit/"]:has-text("{auditName}")</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" t="str">
         <v>E2E Flow 2</v>
       </c>
@@ -3500,7 +3511,7 @@
         <v>Assign Cointrol to user</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" t="str">
         <v>TC-1</v>
       </c>
@@ -3523,7 +3534,7 @@
         <v>a[href*="/audit/"] (home page tiles)</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" t="str">
         <v>TC-2</v>
       </c>
@@ -3543,7 +3554,7 @@
         <v>a[href*="/audit/"].count() &gt; 0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" t="str">
         <v>TC-3</v>
       </c>
@@ -3563,7 +3574,7 @@
         <v>input[placeholder*="Search"]</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" t="str">
         <v>TC-4</v>
       </c>
@@ -3586,7 +3597,7 @@
         <v>input[placeholder*="Search"].fill() → a[href*="/audit/"]</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" t="str">
         <v>TC-5</v>
       </c>
@@ -3609,7 +3620,7 @@
         <v>[role="tab"]:has-text("Workspace") → button:has-text("All Controls")</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" t="str">
         <v>TC-6</v>
       </c>
@@ -3632,7 +3643,7 @@
         <v>table thead tr (columns: Control ID, Owner, Status, Due Date)</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" t="str">
         <v>TC-7</v>
       </c>
@@ -3655,7 +3666,7 @@
         <v>button:has-text("+ Assign")</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" t="str">
         <v>TC-8</v>
       </c>
@@ -3678,7 +3689,7 @@
         <v>td:first-child (Control ID from same row)</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" t="str">
         <v>TC-9</v>
       </c>
@@ -3701,7 +3712,7 @@
         <v>[role="listbox"] or [role="menu"] (dropdown)</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" t="str">
         <v>TC-10</v>
       </c>
@@ -3724,7 +3735,7 @@
         <v>input[placeholder*="search"] (inside dropdown)</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" t="str">
         <v>TC-11</v>
       </c>
@@ -3747,7 +3758,7 @@
         <v>input.fill("Admin") → filter users</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" t="str">
         <v>TC-12</v>
       </c>
@@ -3770,7 +3781,7 @@
         <v>[role="option"]:has-text("Matrix_Admin")</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" t="str">
         <v>TC-13</v>
       </c>
@@ -3793,7 +3804,7 @@
         <v>[role="tab"]:has-text("Controls I Own") → table tbody tr.count() &gt; 0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" t="str">
         <v>TC-14</v>
       </c>
@@ -3816,22 +3827,22 @@
         <v>table tbody tr:nth(1).click() → control detail panel</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" t="str">
         <v>TC-15</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" t="str">
         <v>TC-16</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" t="str">
         <v>TC-17</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" t="str">
         <v>TC-18</v>
       </c>
@@ -3848,7 +3859,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H32"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="str">
         <v>Page</v>
       </c>
@@ -3874,7 +3885,7 @@
         <v>Last Checked</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="str">
         <v>Home</v>
       </c>
@@ -3900,7 +3911,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -3926,7 +3937,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -3952,7 +3963,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -3978,7 +3989,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -4004,7 +4015,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -4030,7 +4041,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -4056,7 +4067,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -4082,7 +4093,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -4108,7 +4119,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -4134,7 +4145,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -4160,7 +4171,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -4186,7 +4197,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" t="str">
         <v>Admin &gt; Integrations</v>
       </c>
@@ -4212,7 +4223,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" t="str">
         <v>Audit Groups</v>
       </c>
@@ -4238,7 +4249,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" t="str">
         <v>Pulse</v>
       </c>
@@ -4264,7 +4275,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" t="str">
         <v>Policies</v>
       </c>
@@ -4290,7 +4301,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" t="str">
         <v>Analytics</v>
       </c>
@@ -4316,7 +4327,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" t="str">
         <v>Reports</v>
       </c>
@@ -4342,7 +4353,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" t="str">
         <v>Integrations</v>
       </c>
@@ -4368,7 +4379,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" t="str">
         <v>Policy to Control Analyzer</v>
       </c>
@@ -4394,7 +4405,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" t="str">
         <v>Guides</v>
       </c>
@@ -4420,7 +4431,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" t="str">
         <v>Admin &gt; Users</v>
       </c>
@@ -4446,7 +4457,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" t="str">
         <v>Admin &gt; Roles</v>
       </c>
@@ -4472,7 +4483,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" t="str">
         <v>Admin &gt; Frameworks</v>
       </c>
@@ -4498,7 +4509,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" t="str">
         <v>Admin &gt; Business Units</v>
       </c>
@@ -4524,7 +4535,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" t="str">
         <v>Admin &gt; Features</v>
       </c>
@@ -4550,7 +4561,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" t="str">
         <v>Admin &gt; API Keys</v>
       </c>
@@ -4576,7 +4587,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" t="str">
         <v>Admin &gt; Activity Log</v>
       </c>
@@ -4602,7 +4613,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" t="str">
         <v>Admin &gt; Organization</v>
       </c>
@@ -4628,7 +4639,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" t="str">
         <v>Admin &gt; SSO</v>
       </c>
@@ -4654,7 +4665,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" t="str">
         <v>Audit Detail</v>
       </c>
@@ -4692,7 +4703,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J489"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="str">
         <v>#</v>
       </c>
@@ -4724,7 +4735,7 @@
         <v>Last Run</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4756,7 +4767,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4788,7 +4799,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4820,7 +4831,7 @@
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4852,7 +4863,7 @@
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4884,7 +4895,7 @@
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4916,7 +4927,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4948,7 +4959,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4980,7 +4991,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5012,7 +5023,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5044,7 +5055,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5076,7 +5087,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5108,7 +5119,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5140,7 +5151,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5172,7 +5183,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5204,7 +5215,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5236,7 +5247,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5268,7 +5279,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5300,7 +5311,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5332,7 +5343,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5364,7 +5375,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5396,7 +5407,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5428,7 +5439,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5460,7 +5471,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5492,7 +5503,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5524,7 +5535,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5556,7 +5567,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5588,7 +5599,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5620,7 +5631,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5652,7 +5663,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5684,7 +5695,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5716,7 +5727,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5748,7 +5759,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5780,7 +5791,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5812,7 +5823,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5844,7 +5855,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5876,7 +5887,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5908,7 +5919,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5940,7 +5951,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5972,7 +5983,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6004,7 +6015,7 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6036,7 +6047,7 @@
         <v/>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6068,7 +6079,7 @@
         <v/>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6100,7 +6111,7 @@
         <v/>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6132,7 +6143,7 @@
         <v/>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6164,7 +6175,7 @@
         <v/>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6196,7 +6207,7 @@
         <v/>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6228,7 +6239,7 @@
         <v/>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6260,7 +6271,7 @@
         <v/>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6292,7 +6303,7 @@
         <v/>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6324,7 +6335,7 @@
         <v/>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6356,7 +6367,7 @@
         <v/>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6388,7 +6399,7 @@
         <v/>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6420,7 +6431,7 @@
         <v/>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6452,7 +6463,7 @@
         <v/>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6484,7 +6495,7 @@
         <v/>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6516,7 +6527,7 @@
         <v/>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6548,7 +6559,7 @@
         <v/>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6580,7 +6591,7 @@
         <v/>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6612,7 +6623,7 @@
         <v/>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6644,7 +6655,7 @@
         <v/>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6676,7 +6687,7 @@
         <v/>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6708,7 +6719,7 @@
         <v/>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6740,7 +6751,7 @@
         <v/>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6772,7 +6783,7 @@
         <v/>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6804,7 +6815,7 @@
         <v/>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6836,7 +6847,7 @@
         <v/>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6868,7 +6879,7 @@
         <v/>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6900,7 +6911,7 @@
         <v/>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6932,7 +6943,7 @@
         <v/>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6964,7 +6975,7 @@
         <v/>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6996,7 +7007,7 @@
         <v/>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7028,7 +7039,7 @@
         <v/>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7060,7 +7071,7 @@
         <v/>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7092,7 +7103,7 @@
         <v/>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7124,7 +7135,7 @@
         <v/>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7156,7 +7167,7 @@
         <v/>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7188,7 +7199,7 @@
         <v/>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7220,7 +7231,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7252,7 +7263,7 @@
         <v/>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7284,7 +7295,7 @@
         <v/>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7316,7 +7327,7 @@
         <v/>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7348,7 +7359,7 @@
         <v/>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7380,7 +7391,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7412,7 +7423,7 @@
         <v/>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7444,7 +7455,7 @@
         <v/>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7476,7 +7487,7 @@
         <v/>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7508,7 +7519,7 @@
         <v/>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7540,7 +7551,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7572,7 +7583,7 @@
         <v/>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7604,7 +7615,7 @@
         <v/>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7636,7 +7647,7 @@
         <v/>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7668,7 +7679,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7700,7 +7711,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7732,7 +7743,7 @@
         <v/>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7764,7 +7775,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7796,7 +7807,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7828,7 +7839,7 @@
         <v/>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7860,7 +7871,7 @@
         <v/>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7892,7 +7903,7 @@
         <v/>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7924,7 +7935,7 @@
         <v/>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7956,7 +7967,7 @@
         <v/>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7988,7 +7999,7 @@
         <v/>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8020,7 +8031,7 @@
         <v/>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8052,7 +8063,7 @@
         <v/>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8084,7 +8095,7 @@
         <v/>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8116,7 +8127,7 @@
         <v/>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8148,7 +8159,7 @@
         <v/>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8180,7 +8191,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8212,7 +8223,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8244,7 +8255,7 @@
         <v/>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8276,7 +8287,7 @@
         <v/>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8308,7 +8319,7 @@
         <v/>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8340,7 +8351,7 @@
         <v/>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8372,7 +8383,7 @@
         <v/>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8404,7 +8415,7 @@
         <v/>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8436,7 +8447,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8468,7 +8479,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8500,7 +8511,7 @@
         <v/>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8532,7 +8543,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8564,7 +8575,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8596,7 +8607,7 @@
         <v/>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8628,7 +8639,7 @@
         <v/>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8660,7 +8671,7 @@
         <v/>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8692,7 +8703,7 @@
         <v/>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126">
         <v>125</v>
       </c>
@@ -8724,7 +8735,7 @@
         <v/>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127">
         <v>126</v>
       </c>
@@ -8756,7 +8767,7 @@
         <v/>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8788,7 +8799,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129">
         <v>128</v>
       </c>
@@ -8820,7 +8831,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130">
         <v>129</v>
       </c>
@@ -8852,7 +8863,7 @@
         <v/>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131">
         <v>130</v>
       </c>
@@ -8884,7 +8895,7 @@
         <v/>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132">
         <v>131</v>
       </c>
@@ -8916,7 +8927,7 @@
         <v/>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133">
         <v>132</v>
       </c>
@@ -8948,7 +8959,7 @@
         <v/>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134">
         <v>133</v>
       </c>
@@ -8980,7 +8991,7 @@
         <v/>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135">
         <v>134</v>
       </c>
@@ -9012,7 +9023,7 @@
         <v/>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136">
         <v>135</v>
       </c>
@@ -9044,7 +9055,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137">
         <v>136</v>
       </c>
@@ -9076,7 +9087,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138">
         <v>137</v>
       </c>
@@ -9108,7 +9119,7 @@
         <v/>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139">
         <v>138</v>
       </c>
@@ -9140,7 +9151,7 @@
         <v/>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140">
         <v>139</v>
       </c>
@@ -9172,7 +9183,7 @@
         <v/>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141">
         <v>140</v>
       </c>
@@ -9204,7 +9215,7 @@
         <v/>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142">
         <v>141</v>
       </c>
@@ -9236,7 +9247,7 @@
         <v/>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143">
         <v>142</v>
       </c>
@@ -9268,7 +9279,7 @@
         <v/>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144">
         <v>143</v>
       </c>
@@ -9300,7 +9311,7 @@
         <v/>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145">
         <v>144</v>
       </c>
@@ -9332,7 +9343,7 @@
         <v/>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146">
         <v>145</v>
       </c>
@@ -9364,7 +9375,7 @@
         <v/>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147">
         <v>146</v>
       </c>
@@ -9396,7 +9407,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148">
         <v>147</v>
       </c>
@@ -9428,7 +9439,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149">
         <v>148</v>
       </c>
@@ -9460,7 +9471,7 @@
         <v/>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150">
         <v>149</v>
       </c>
@@ -9492,7 +9503,7 @@
         <v/>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151">
         <v>150</v>
       </c>
@@ -9524,7 +9535,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152">
         <v>151</v>
       </c>
@@ -9556,7 +9567,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153">
         <v>152</v>
       </c>
@@ -9588,7 +9599,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154">
         <v>153</v>
       </c>
@@ -9620,7 +9631,7 @@
         <v/>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155">
         <v>154</v>
       </c>
@@ -9652,7 +9663,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156">
         <v>155</v>
       </c>
@@ -9684,7 +9695,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157">
         <v>156</v>
       </c>
@@ -9716,7 +9727,7 @@
         <v/>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158">
         <v>157</v>
       </c>
@@ -9748,7 +9759,7 @@
         <v/>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159">
         <v>158</v>
       </c>
@@ -9780,7 +9791,7 @@
         <v/>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160">
         <v>159</v>
       </c>
@@ -9812,7 +9823,7 @@
         <v/>
       </c>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161">
         <v>160</v>
       </c>
@@ -9844,7 +9855,7 @@
         <v/>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162">
         <v>161</v>
       </c>
@@ -9876,7 +9887,7 @@
         <v/>
       </c>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163">
         <v>162</v>
       </c>
@@ -9908,7 +9919,7 @@
         <v/>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164">
         <v>163</v>
       </c>
@@ -9940,7 +9951,7 @@
         <v/>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165">
         <v>164</v>
       </c>
@@ -9972,7 +9983,7 @@
         <v/>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166">
         <v>165</v>
       </c>
@@ -10004,7 +10015,7 @@
         <v/>
       </c>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167">
         <v>166</v>
       </c>
@@ -10036,7 +10047,7 @@
         <v/>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168">
         <v>167</v>
       </c>
@@ -10068,7 +10079,7 @@
         <v/>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169">
         <v>168</v>
       </c>
@@ -10100,7 +10111,7 @@
         <v/>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170">
         <v>169</v>
       </c>
@@ -10132,7 +10143,7 @@
         <v/>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171">
         <v>170</v>
       </c>
@@ -10164,7 +10175,7 @@
         <v/>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172">
         <v>171</v>
       </c>
@@ -10196,7 +10207,7 @@
         <v/>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173">
         <v>172</v>
       </c>
@@ -10228,7 +10239,7 @@
         <v/>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174">
         <v>173</v>
       </c>
@@ -10260,7 +10271,7 @@
         <v/>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175">
         <v>174</v>
       </c>
@@ -10292,7 +10303,7 @@
         <v/>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176">
         <v>175</v>
       </c>
@@ -10324,7 +10335,7 @@
         <v/>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177">
         <v>176</v>
       </c>
@@ -10356,7 +10367,7 @@
         <v/>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178">
         <v>177</v>
       </c>
@@ -10388,7 +10399,7 @@
         <v/>
       </c>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179">
         <v>178</v>
       </c>
@@ -10420,7 +10431,7 @@
         <v/>
       </c>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180">
         <v>179</v>
       </c>
@@ -10452,7 +10463,7 @@
         <v/>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181">
         <v>180</v>
       </c>
@@ -10484,7 +10495,7 @@
         <v/>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182">
         <v>181</v>
       </c>
@@ -10516,7 +10527,7 @@
         <v/>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183">
         <v>182</v>
       </c>
@@ -10548,7 +10559,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184">
         <v>183</v>
       </c>
@@ -10580,7 +10591,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185">
         <v>184</v>
       </c>
@@ -10612,7 +10623,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186">
         <v>185</v>
       </c>
@@ -10644,7 +10655,7 @@
         <v/>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187">
         <v>186</v>
       </c>
@@ -10676,7 +10687,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188">
         <v>187</v>
       </c>
@@ -10708,7 +10719,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189">
         <v>188</v>
       </c>
@@ -10740,7 +10751,7 @@
         <v/>
       </c>
     </row>
-    <row r="190">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190">
         <v>189</v>
       </c>
@@ -10772,7 +10783,7 @@
         <v/>
       </c>
     </row>
-    <row r="191">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191">
         <v>190</v>
       </c>
@@ -10804,7 +10815,7 @@
         <v/>
       </c>
     </row>
-    <row r="192">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192">
         <v>191</v>
       </c>
@@ -10836,7 +10847,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193">
         <v>192</v>
       </c>
@@ -10868,7 +10879,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194">
         <v>193</v>
       </c>
@@ -10900,7 +10911,7 @@
         <v/>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195">
         <v>194</v>
       </c>
@@ -10932,7 +10943,7 @@
         <v/>
       </c>
     </row>
-    <row r="196">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196">
         <v>195</v>
       </c>
@@ -10964,7 +10975,7 @@
         <v/>
       </c>
     </row>
-    <row r="197">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197">
         <v>196</v>
       </c>
@@ -10996,7 +11007,7 @@
         <v/>
       </c>
     </row>
-    <row r="198">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198">
         <v>197</v>
       </c>
@@ -11028,7 +11039,7 @@
         <v/>
       </c>
     </row>
-    <row r="199">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199">
         <v>198</v>
       </c>
@@ -11060,7 +11071,7 @@
         <v/>
       </c>
     </row>
-    <row r="200">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200">
         <v>199</v>
       </c>
@@ -11092,7 +11103,7 @@
         <v/>
       </c>
     </row>
-    <row r="201">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201">
         <v>200</v>
       </c>
@@ -11124,7 +11135,7 @@
         <v/>
       </c>
     </row>
-    <row r="202">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202">
         <v>201</v>
       </c>
@@ -11156,7 +11167,7 @@
         <v/>
       </c>
     </row>
-    <row r="203">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203">
         <v>202</v>
       </c>
@@ -11188,7 +11199,7 @@
         <v/>
       </c>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204">
         <v>203</v>
       </c>
@@ -11220,7 +11231,7 @@
         <v/>
       </c>
     </row>
-    <row r="205">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205">
         <v>204</v>
       </c>
@@ -11252,7 +11263,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206">
         <v>205</v>
       </c>
@@ -11284,7 +11295,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207">
         <v>206</v>
       </c>
@@ -11316,7 +11327,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208">
         <v>207</v>
       </c>
@@ -11348,7 +11359,7 @@
         <v/>
       </c>
     </row>
-    <row r="209">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209">
         <v>208</v>
       </c>
@@ -11380,7 +11391,7 @@
         <v/>
       </c>
     </row>
-    <row r="210">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210">
         <v>209</v>
       </c>
@@ -11412,7 +11423,7 @@
         <v/>
       </c>
     </row>
-    <row r="211">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211">
         <v>210</v>
       </c>
@@ -11444,7 +11455,7 @@
         <v/>
       </c>
     </row>
-    <row r="212">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212">
         <v>211</v>
       </c>
@@ -11476,7 +11487,7 @@
         <v/>
       </c>
     </row>
-    <row r="213">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213">
         <v>212</v>
       </c>
@@ -11508,7 +11519,7 @@
         <v/>
       </c>
     </row>
-    <row r="214">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214">
         <v>213</v>
       </c>
@@ -11540,7 +11551,7 @@
         <v/>
       </c>
     </row>
-    <row r="215">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215">
         <v>214</v>
       </c>
@@ -11572,7 +11583,7 @@
         <v/>
       </c>
     </row>
-    <row r="216">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216">
         <v>215</v>
       </c>
@@ -11604,7 +11615,7 @@
         <v/>
       </c>
     </row>
-    <row r="217">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217">
         <v>216</v>
       </c>
@@ -11636,7 +11647,7 @@
         <v/>
       </c>
     </row>
-    <row r="218">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218">
         <v>217</v>
       </c>
@@ -11668,7 +11679,7 @@
         <v/>
       </c>
     </row>
-    <row r="219">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219">
         <v>218</v>
       </c>
@@ -11700,7 +11711,7 @@
         <v/>
       </c>
     </row>
-    <row r="220">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220">
         <v>219</v>
       </c>
@@ -11732,7 +11743,7 @@
         <v/>
       </c>
     </row>
-    <row r="221">
+    <row r="221" ht="15.75" customHeight="1">
       <c r="A221">
         <v>220</v>
       </c>
@@ -11764,7 +11775,7 @@
         <v/>
       </c>
     </row>
-    <row r="222">
+    <row r="222" ht="15.75" customHeight="1">
       <c r="A222">
         <v>221</v>
       </c>
@@ -11796,7 +11807,7 @@
         <v/>
       </c>
     </row>
-    <row r="223">
+    <row r="223" ht="15.75" customHeight="1">
       <c r="A223">
         <v>222</v>
       </c>
@@ -11828,7 +11839,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" ht="15.75" customHeight="1">
       <c r="A224">
         <v>223</v>
       </c>
@@ -11860,7 +11871,7 @@
         <v/>
       </c>
     </row>
-    <row r="225">
+    <row r="225" ht="15.75" customHeight="1">
       <c r="A225">
         <v>224</v>
       </c>
@@ -11892,7 +11903,7 @@
         <v/>
       </c>
     </row>
-    <row r="226">
+    <row r="226" ht="15.75" customHeight="1">
       <c r="A226">
         <v>225</v>
       </c>
@@ -11924,7 +11935,7 @@
         <v/>
       </c>
     </row>
-    <row r="227">
+    <row r="227" ht="15.75" customHeight="1">
       <c r="A227">
         <v>226</v>
       </c>
@@ -11956,7 +11967,7 @@
         <v/>
       </c>
     </row>
-    <row r="228">
+    <row r="228" ht="15.75" customHeight="1">
       <c r="A228">
         <v>227</v>
       </c>
@@ -11988,7 +11999,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" ht="15.75" customHeight="1">
       <c r="A229">
         <v>228</v>
       </c>
@@ -12020,7 +12031,7 @@
         <v/>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="15.75" customHeight="1">
       <c r="A230">
         <v>229</v>
       </c>
@@ -12052,7 +12063,7 @@
         <v/>
       </c>
     </row>
-    <row r="231">
+    <row r="231" ht="15.75" customHeight="1">
       <c r="A231">
         <v>230</v>
       </c>
@@ -12084,7 +12095,7 @@
         <v/>
       </c>
     </row>
-    <row r="232">
+    <row r="232" ht="15.75" customHeight="1">
       <c r="A232">
         <v>231</v>
       </c>
@@ -12116,7 +12127,7 @@
         <v/>
       </c>
     </row>
-    <row r="233">
+    <row r="233" ht="15.75" customHeight="1">
       <c r="A233">
         <v>232</v>
       </c>
@@ -12148,7 +12159,7 @@
         <v/>
       </c>
     </row>
-    <row r="234">
+    <row r="234" ht="15.75" customHeight="1">
       <c r="A234">
         <v>233</v>
       </c>
@@ -12180,7 +12191,7 @@
         <v/>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="15.75" customHeight="1">
       <c r="A235">
         <v>234</v>
       </c>
@@ -12212,7 +12223,7 @@
         <v/>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="15.75" customHeight="1">
       <c r="A236">
         <v>235</v>
       </c>
@@ -12244,7 +12255,7 @@
         <v/>
       </c>
     </row>
-    <row r="237">
+    <row r="237" ht="15.75" customHeight="1">
       <c r="A237">
         <v>236</v>
       </c>
@@ -12276,7 +12287,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" ht="15.75" customHeight="1">
       <c r="A238">
         <v>237</v>
       </c>
@@ -12308,7 +12319,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" ht="15.75" customHeight="1">
       <c r="A239">
         <v>238</v>
       </c>
@@ -12340,7 +12351,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" ht="15.75" customHeight="1">
       <c r="A240">
         <v>239</v>
       </c>
@@ -12372,7 +12383,7 @@
         <v/>
       </c>
     </row>
-    <row r="241">
+    <row r="241" ht="15.75" customHeight="1">
       <c r="A241">
         <v>240</v>
       </c>
@@ -12404,7 +12415,7 @@
         <v/>
       </c>
     </row>
-    <row r="242">
+    <row r="242" ht="15.75" customHeight="1">
       <c r="A242">
         <v>241</v>
       </c>
@@ -12436,7 +12447,7 @@
         <v/>
       </c>
     </row>
-    <row r="243">
+    <row r="243" ht="15.75" customHeight="1">
       <c r="A243">
         <v>242</v>
       </c>
@@ -12468,7 +12479,7 @@
         <v/>
       </c>
     </row>
-    <row r="244">
+    <row r="244" ht="15.75" customHeight="1">
       <c r="A244">
         <v>243</v>
       </c>
@@ -12500,7 +12511,7 @@
         <v/>
       </c>
     </row>
-    <row r="245">
+    <row r="245" ht="15.75" customHeight="1">
       <c r="A245">
         <v>244</v>
       </c>
@@ -12532,7 +12543,7 @@
         <v/>
       </c>
     </row>
-    <row r="246">
+    <row r="246" ht="15.75" customHeight="1">
       <c r="A246">
         <v>245</v>
       </c>
@@ -12564,7 +12575,7 @@
         <v/>
       </c>
     </row>
-    <row r="247">
+    <row r="247" ht="15.75" customHeight="1">
       <c r="A247">
         <v>246</v>
       </c>
@@ -12596,7 +12607,7 @@
         <v/>
       </c>
     </row>
-    <row r="248">
+    <row r="248" ht="15.75" customHeight="1">
       <c r="A248">
         <v>247</v>
       </c>
@@ -12628,7 +12639,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" ht="15.75" customHeight="1">
       <c r="A249">
         <v>248</v>
       </c>
@@ -12660,7 +12671,7 @@
         <v/>
       </c>
     </row>
-    <row r="250">
+    <row r="250" ht="15.75" customHeight="1">
       <c r="A250">
         <v>249</v>
       </c>
@@ -12692,7 +12703,7 @@
         <v/>
       </c>
     </row>
-    <row r="251">
+    <row r="251" ht="15.75" customHeight="1">
       <c r="A251">
         <v>250</v>
       </c>
@@ -12724,7 +12735,7 @@
         <v/>
       </c>
     </row>
-    <row r="252">
+    <row r="252" ht="15.75" customHeight="1">
       <c r="A252">
         <v>251</v>
       </c>
@@ -12756,7 +12767,7 @@
         <v/>
       </c>
     </row>
-    <row r="253">
+    <row r="253" ht="15.75" customHeight="1">
       <c r="A253">
         <v>252</v>
       </c>
@@ -12788,7 +12799,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" ht="15.75" customHeight="1">
       <c r="A254">
         <v>253</v>
       </c>
@@ -12820,7 +12831,7 @@
         <v/>
       </c>
     </row>
-    <row r="255">
+    <row r="255" ht="15.75" customHeight="1">
       <c r="A255">
         <v>254</v>
       </c>
@@ -12852,7 +12863,7 @@
         <v/>
       </c>
     </row>
-    <row r="256">
+    <row r="256" ht="15.75" customHeight="1">
       <c r="A256">
         <v>255</v>
       </c>
@@ -12884,7 +12895,7 @@
         <v/>
       </c>
     </row>
-    <row r="257">
+    <row r="257" ht="15.75" customHeight="1">
       <c r="A257">
         <v>256</v>
       </c>
@@ -12916,7 +12927,7 @@
         <v/>
       </c>
     </row>
-    <row r="258">
+    <row r="258" ht="15.75" customHeight="1">
       <c r="A258">
         <v>257</v>
       </c>
@@ -12948,7 +12959,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" ht="15.75" customHeight="1">
       <c r="A259">
         <v>258</v>
       </c>
@@ -12980,7 +12991,7 @@
         <v/>
       </c>
     </row>
-    <row r="260">
+    <row r="260" ht="15.75" customHeight="1">
       <c r="A260">
         <v>259</v>
       </c>
@@ -13012,7 +13023,7 @@
         <v/>
       </c>
     </row>
-    <row r="261">
+    <row r="261" ht="15.75" customHeight="1">
       <c r="A261">
         <v>260</v>
       </c>
@@ -13044,7 +13055,7 @@
         <v/>
       </c>
     </row>
-    <row r="262">
+    <row r="262" ht="15.75" customHeight="1">
       <c r="A262">
         <v>261</v>
       </c>
@@ -13076,7 +13087,7 @@
         <v/>
       </c>
     </row>
-    <row r="263">
+    <row r="263" ht="15.75" customHeight="1">
       <c r="A263">
         <v>262</v>
       </c>
@@ -13108,7 +13119,7 @@
         <v/>
       </c>
     </row>
-    <row r="264">
+    <row r="264" ht="15.75" customHeight="1">
       <c r="A264">
         <v>263</v>
       </c>
@@ -13140,7 +13151,7 @@
         <v/>
       </c>
     </row>
-    <row r="265">
+    <row r="265" ht="15.75" customHeight="1">
       <c r="A265">
         <v>264</v>
       </c>
@@ -13172,7 +13183,7 @@
         <v/>
       </c>
     </row>
-    <row r="266">
+    <row r="266" ht="15.75" customHeight="1">
       <c r="A266">
         <v>265</v>
       </c>
@@ -13204,7 +13215,7 @@
         <v/>
       </c>
     </row>
-    <row r="267">
+    <row r="267" ht="15.75" customHeight="1">
       <c r="A267">
         <v>266</v>
       </c>
@@ -13236,7 +13247,7 @@
         <v/>
       </c>
     </row>
-    <row r="268">
+    <row r="268" ht="15.75" customHeight="1">
       <c r="A268">
         <v>267</v>
       </c>
@@ -13268,7 +13279,7 @@
         <v/>
       </c>
     </row>
-    <row r="269">
+    <row r="269" ht="15.75" customHeight="1">
       <c r="A269">
         <v>268</v>
       </c>
@@ -13300,7 +13311,7 @@
         <v/>
       </c>
     </row>
-    <row r="270">
+    <row r="270" ht="15.75" customHeight="1">
       <c r="A270">
         <v>269</v>
       </c>
@@ -13332,7 +13343,7 @@
         <v/>
       </c>
     </row>
-    <row r="271">
+    <row r="271" ht="15.75" customHeight="1">
       <c r="A271">
         <v>270</v>
       </c>
@@ -13364,7 +13375,7 @@
         <v/>
       </c>
     </row>
-    <row r="272">
+    <row r="272" ht="15.75" customHeight="1">
       <c r="A272">
         <v>271</v>
       </c>
@@ -13396,7 +13407,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" ht="15.75" customHeight="1">
       <c r="A273">
         <v>272</v>
       </c>
@@ -13428,7 +13439,7 @@
         <v/>
       </c>
     </row>
-    <row r="274">
+    <row r="274" ht="15.75" customHeight="1">
       <c r="A274">
         <v>273</v>
       </c>
@@ -13460,7 +13471,7 @@
         <v/>
       </c>
     </row>
-    <row r="275">
+    <row r="275" ht="15.75" customHeight="1">
       <c r="A275">
         <v>274</v>
       </c>
@@ -13492,7 +13503,7 @@
         <v/>
       </c>
     </row>
-    <row r="276">
+    <row r="276" ht="15.75" customHeight="1">
       <c r="A276">
         <v>275</v>
       </c>
@@ -13524,7 +13535,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" ht="15.75" customHeight="1">
       <c r="A277">
         <v>276</v>
       </c>
@@ -13556,7 +13567,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" ht="15.75" customHeight="1">
       <c r="A278">
         <v>277</v>
       </c>
@@ -13588,7 +13599,7 @@
         <v/>
       </c>
     </row>
-    <row r="279">
+    <row r="279" ht="15.75" customHeight="1">
       <c r="A279">
         <v>278</v>
       </c>
@@ -13620,7 +13631,7 @@
         <v/>
       </c>
     </row>
-    <row r="280">
+    <row r="280" ht="15.75" customHeight="1">
       <c r="A280">
         <v>279</v>
       </c>
@@ -13652,7 +13663,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" ht="15.75" customHeight="1">
       <c r="A281">
         <v>280</v>
       </c>
@@ -13684,7 +13695,7 @@
         <v/>
       </c>
     </row>
-    <row r="282">
+    <row r="282" ht="15.75" customHeight="1">
       <c r="A282">
         <v>281</v>
       </c>
@@ -13716,7 +13727,7 @@
         <v/>
       </c>
     </row>
-    <row r="283">
+    <row r="283" ht="15.75" customHeight="1">
       <c r="A283">
         <v>282</v>
       </c>
@@ -13748,7 +13759,7 @@
         <v/>
       </c>
     </row>
-    <row r="284">
+    <row r="284" ht="15.75" customHeight="1">
       <c r="A284">
         <v>283</v>
       </c>
@@ -13780,7 +13791,7 @@
         <v/>
       </c>
     </row>
-    <row r="285">
+    <row r="285" ht="15.75" customHeight="1">
       <c r="A285">
         <v>284</v>
       </c>
@@ -13812,7 +13823,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" ht="15.75" customHeight="1">
       <c r="A286">
         <v>285</v>
       </c>
@@ -13844,7 +13855,7 @@
         <v/>
       </c>
     </row>
-    <row r="287">
+    <row r="287" ht="15.75" customHeight="1">
       <c r="A287">
         <v>286</v>
       </c>
@@ -13876,7 +13887,7 @@
         <v/>
       </c>
     </row>
-    <row r="288">
+    <row r="288" ht="15.75" customHeight="1">
       <c r="A288">
         <v>287</v>
       </c>
@@ -13908,7 +13919,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" ht="15.75" customHeight="1">
       <c r="A289">
         <v>288</v>
       </c>
@@ -13940,7 +13951,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" ht="15.75" customHeight="1">
       <c r="A290">
         <v>289</v>
       </c>
@@ -13972,7 +13983,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" ht="15.75" customHeight="1">
       <c r="A291">
         <v>290</v>
       </c>
@@ -14004,7 +14015,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" ht="15.75" customHeight="1">
       <c r="A292">
         <v>291</v>
       </c>
@@ -14036,7 +14047,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" ht="15.75" customHeight="1">
       <c r="A293">
         <v>292</v>
       </c>
@@ -14068,7 +14079,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" ht="15.75" customHeight="1">
       <c r="A294">
         <v>293</v>
       </c>
@@ -14100,7 +14111,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" ht="15.75" customHeight="1">
       <c r="A295">
         <v>294</v>
       </c>
@@ -14132,7 +14143,7 @@
         <v/>
       </c>
     </row>
-    <row r="296">
+    <row r="296" ht="15.75" customHeight="1">
       <c r="A296">
         <v>295</v>
       </c>
@@ -14164,7 +14175,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" ht="15.75" customHeight="1">
       <c r="A297">
         <v>296</v>
       </c>
@@ -14196,7 +14207,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" ht="15.75" customHeight="1">
       <c r="A298">
         <v>297</v>
       </c>
@@ -14228,7 +14239,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" ht="15.75" customHeight="1">
       <c r="A299">
         <v>298</v>
       </c>
@@ -14260,7 +14271,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" ht="15.75" customHeight="1">
       <c r="A300">
         <v>299</v>
       </c>
@@ -14292,7 +14303,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" ht="15.75" customHeight="1">
       <c r="A301">
         <v>300</v>
       </c>
@@ -14324,7 +14335,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" ht="15.75" customHeight="1">
       <c r="A302">
         <v>301</v>
       </c>
@@ -14356,7 +14367,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" ht="15.75" customHeight="1">
       <c r="A303">
         <v>302</v>
       </c>
@@ -14388,7 +14399,7 @@
         <v/>
       </c>
     </row>
-    <row r="304">
+    <row r="304" ht="15.75" customHeight="1">
       <c r="A304">
         <v>303</v>
       </c>
@@ -14420,7 +14431,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" ht="15.75" customHeight="1">
       <c r="A305">
         <v>304</v>
       </c>
@@ -14452,7 +14463,7 @@
         <v/>
       </c>
     </row>
-    <row r="306">
+    <row r="306" ht="15.75" customHeight="1">
       <c r="A306">
         <v>305</v>
       </c>
@@ -14484,7 +14495,7 @@
         <v/>
       </c>
     </row>
-    <row r="307">
+    <row r="307" ht="15.75" customHeight="1">
       <c r="A307">
         <v>306</v>
       </c>
@@ -14516,7 +14527,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" ht="15.75" customHeight="1">
       <c r="A308">
         <v>307</v>
       </c>
@@ -14548,7 +14559,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" ht="15.75" customHeight="1">
       <c r="A309">
         <v>308</v>
       </c>
@@ -14580,7 +14591,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" ht="15.75" customHeight="1">
       <c r="A310">
         <v>309</v>
       </c>
@@ -14612,7 +14623,7 @@
         <v/>
       </c>
     </row>
-    <row r="311">
+    <row r="311" ht="15.75" customHeight="1">
       <c r="A311">
         <v>310</v>
       </c>
@@ -14644,7 +14655,7 @@
         <v/>
       </c>
     </row>
-    <row r="312">
+    <row r="312" ht="15.75" customHeight="1">
       <c r="A312">
         <v>311</v>
       </c>
@@ -14676,7 +14687,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" ht="15.75" customHeight="1">
       <c r="A313">
         <v>312</v>
       </c>
@@ -14708,7 +14719,7 @@
         <v/>
       </c>
     </row>
-    <row r="314">
+    <row r="314" ht="15.75" customHeight="1">
       <c r="A314">
         <v>313</v>
       </c>
@@ -14740,7 +14751,7 @@
         <v/>
       </c>
     </row>
-    <row r="315">
+    <row r="315" ht="15.75" customHeight="1">
       <c r="A315">
         <v>314</v>
       </c>
@@ -14772,7 +14783,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" ht="15.75" customHeight="1">
       <c r="A316">
         <v>315</v>
       </c>
@@ -14804,7 +14815,7 @@
         <v/>
       </c>
     </row>
-    <row r="317">
+    <row r="317" ht="15.75" customHeight="1">
       <c r="A317">
         <v>316</v>
       </c>
@@ -14836,7 +14847,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" ht="15.75" customHeight="1">
       <c r="A318">
         <v>317</v>
       </c>
@@ -14868,7 +14879,7 @@
         <v/>
       </c>
     </row>
-    <row r="319">
+    <row r="319" ht="15.75" customHeight="1">
       <c r="A319">
         <v>318</v>
       </c>
@@ -14900,7 +14911,7 @@
         <v/>
       </c>
     </row>
-    <row r="320">
+    <row r="320" ht="15.75" customHeight="1">
       <c r="A320">
         <v>319</v>
       </c>
@@ -14932,7 +14943,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" ht="15.75" customHeight="1">
       <c r="A321">
         <v>320</v>
       </c>
@@ -14964,7 +14975,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" ht="15.75" customHeight="1">
       <c r="A322">
         <v>321</v>
       </c>
@@ -14996,7 +15007,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" ht="15.75" customHeight="1">
       <c r="A323">
         <v>322</v>
       </c>
@@ -15028,7 +15039,7 @@
         <v/>
       </c>
     </row>
-    <row r="324">
+    <row r="324" ht="15.75" customHeight="1">
       <c r="A324">
         <v>323</v>
       </c>
@@ -15060,7 +15071,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" ht="15.75" customHeight="1">
       <c r="A325">
         <v>324</v>
       </c>
@@ -15092,7 +15103,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" ht="15.75" customHeight="1">
       <c r="A326">
         <v>325</v>
       </c>
@@ -15124,7 +15135,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" ht="15.75" customHeight="1">
       <c r="A327">
         <v>326</v>
       </c>
@@ -15156,7 +15167,7 @@
         <v/>
       </c>
     </row>
-    <row r="328">
+    <row r="328" ht="15.75" customHeight="1">
       <c r="A328">
         <v>327</v>
       </c>
@@ -15188,7 +15199,7 @@
         <v/>
       </c>
     </row>
-    <row r="329">
+    <row r="329" ht="15.75" customHeight="1">
       <c r="A329">
         <v>328</v>
       </c>
@@ -15220,7 +15231,7 @@
         <v/>
       </c>
     </row>
-    <row r="330">
+    <row r="330" ht="15.75" customHeight="1">
       <c r="A330">
         <v>329</v>
       </c>
@@ -15252,7 +15263,7 @@
         <v/>
       </c>
     </row>
-    <row r="331">
+    <row r="331" ht="15.75" customHeight="1">
       <c r="A331">
         <v>330</v>
       </c>
@@ -15284,7 +15295,7 @@
         <v/>
       </c>
     </row>
-    <row r="332">
+    <row r="332" ht="15.75" customHeight="1">
       <c r="A332">
         <v>331</v>
       </c>
@@ -15316,7 +15327,7 @@
         <v/>
       </c>
     </row>
-    <row r="333">
+    <row r="333" ht="15.75" customHeight="1">
       <c r="A333">
         <v>332</v>
       </c>
@@ -15348,7 +15359,7 @@
         <v/>
       </c>
     </row>
-    <row r="334">
+    <row r="334" ht="15.75" customHeight="1">
       <c r="A334">
         <v>333</v>
       </c>
@@ -15380,7 +15391,7 @@
         <v/>
       </c>
     </row>
-    <row r="335">
+    <row r="335" ht="15.75" customHeight="1">
       <c r="A335">
         <v>334</v>
       </c>
@@ -15412,7 +15423,7 @@
         <v/>
       </c>
     </row>
-    <row r="336">
+    <row r="336" ht="15.75" customHeight="1">
       <c r="A336">
         <v>335</v>
       </c>
@@ -15444,7 +15455,7 @@
         <v/>
       </c>
     </row>
-    <row r="337">
+    <row r="337" ht="15.75" customHeight="1">
       <c r="A337">
         <v>336</v>
       </c>
@@ -15476,7 +15487,7 @@
         <v/>
       </c>
     </row>
-    <row r="338">
+    <row r="338" ht="15.75" customHeight="1">
       <c r="A338">
         <v>337</v>
       </c>
@@ -15508,7 +15519,7 @@
         <v/>
       </c>
     </row>
-    <row r="339">
+    <row r="339" ht="15.75" customHeight="1">
       <c r="A339">
         <v>338</v>
       </c>
@@ -15540,7 +15551,7 @@
         <v/>
       </c>
     </row>
-    <row r="340">
+    <row r="340" ht="15.75" customHeight="1">
       <c r="A340">
         <v>339</v>
       </c>
@@ -15572,7 +15583,7 @@
         <v/>
       </c>
     </row>
-    <row r="341">
+    <row r="341" ht="15.75" customHeight="1">
       <c r="A341">
         <v>340</v>
       </c>
@@ -15604,7 +15615,7 @@
         <v/>
       </c>
     </row>
-    <row r="342">
+    <row r="342" ht="15.75" customHeight="1">
       <c r="A342">
         <v>341</v>
       </c>
@@ -15636,7 +15647,7 @@
         <v/>
       </c>
     </row>
-    <row r="343">
+    <row r="343" ht="15.75" customHeight="1">
       <c r="A343">
         <v>342</v>
       </c>
@@ -15668,7 +15679,7 @@
         <v/>
       </c>
     </row>
-    <row r="344">
+    <row r="344" ht="15.75" customHeight="1">
       <c r="A344">
         <v>343</v>
       </c>
@@ -15700,7 +15711,7 @@
         <v/>
       </c>
     </row>
-    <row r="345">
+    <row r="345" ht="15.75" customHeight="1">
       <c r="A345">
         <v>344</v>
       </c>
@@ -15732,7 +15743,7 @@
         <v/>
       </c>
     </row>
-    <row r="346">
+    <row r="346" ht="15.75" customHeight="1">
       <c r="A346">
         <v>345</v>
       </c>
@@ -15764,7 +15775,7 @@
         <v/>
       </c>
     </row>
-    <row r="347">
+    <row r="347" ht="15.75" customHeight="1">
       <c r="A347">
         <v>346</v>
       </c>
@@ -15796,7 +15807,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" ht="15.75" customHeight="1">
       <c r="A348">
         <v>347</v>
       </c>
@@ -15828,7 +15839,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" ht="15.75" customHeight="1">
       <c r="A349">
         <v>348</v>
       </c>
@@ -15860,7 +15871,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" ht="15.75" customHeight="1">
       <c r="A350">
         <v>349</v>
       </c>
@@ -15892,7 +15903,7 @@
         <v/>
       </c>
     </row>
-    <row r="351">
+    <row r="351" ht="15.75" customHeight="1">
       <c r="A351">
         <v>350</v>
       </c>
@@ -15924,7 +15935,7 @@
         <v/>
       </c>
     </row>
-    <row r="352">
+    <row r="352" ht="15.75" customHeight="1">
       <c r="A352">
         <v>351</v>
       </c>
@@ -15956,7 +15967,7 @@
         <v/>
       </c>
     </row>
-    <row r="353">
+    <row r="353" ht="15.75" customHeight="1">
       <c r="A353">
         <v>352</v>
       </c>
@@ -15988,7 +15999,7 @@
         <v/>
       </c>
     </row>
-    <row r="354">
+    <row r="354" ht="15.75" customHeight="1">
       <c r="A354">
         <v>353</v>
       </c>
@@ -16020,7 +16031,7 @@
         <v/>
       </c>
     </row>
-    <row r="355">
+    <row r="355" ht="15.75" customHeight="1">
       <c r="A355">
         <v>354</v>
       </c>
@@ -16052,7 +16063,7 @@
         <v/>
       </c>
     </row>
-    <row r="356">
+    <row r="356" ht="15.75" customHeight="1">
       <c r="A356">
         <v>355</v>
       </c>
@@ -16084,7 +16095,7 @@
         <v/>
       </c>
     </row>
-    <row r="357">
+    <row r="357" ht="15.75" customHeight="1">
       <c r="A357">
         <v>356</v>
       </c>
@@ -16116,7 +16127,7 @@
         <v/>
       </c>
     </row>
-    <row r="358">
+    <row r="358" ht="15.75" customHeight="1">
       <c r="A358">
         <v>357</v>
       </c>
@@ -16148,7 +16159,7 @@
         <v/>
       </c>
     </row>
-    <row r="359">
+    <row r="359" ht="15.75" customHeight="1">
       <c r="A359">
         <v>358</v>
       </c>
@@ -16180,7 +16191,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" ht="15.75" customHeight="1">
       <c r="A360">
         <v>359</v>
       </c>
@@ -16212,7 +16223,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" ht="15.75" customHeight="1">
       <c r="A361">
         <v>360</v>
       </c>
@@ -16244,7 +16255,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" ht="15.75" customHeight="1">
       <c r="A362">
         <v>361</v>
       </c>
@@ -16276,7 +16287,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" ht="15.75" customHeight="1">
       <c r="A363">
         <v>362</v>
       </c>
@@ -16308,7 +16319,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" ht="15.75" customHeight="1">
       <c r="A364">
         <v>363</v>
       </c>
@@ -16340,7 +16351,7 @@
         <v/>
       </c>
     </row>
-    <row r="365">
+    <row r="365" ht="15.75" customHeight="1">
       <c r="A365">
         <v>364</v>
       </c>
@@ -16372,7 +16383,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" ht="15.75" customHeight="1">
       <c r="A366">
         <v>365</v>
       </c>
@@ -16404,7 +16415,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" ht="15.75" customHeight="1">
       <c r="A367">
         <v>366</v>
       </c>
@@ -16436,7 +16447,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" ht="15.75" customHeight="1">
       <c r="A368">
         <v>367</v>
       </c>
@@ -16468,7 +16479,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" ht="15.75" customHeight="1">
       <c r="A369">
         <v>368</v>
       </c>
@@ -16500,7 +16511,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" ht="15.75" customHeight="1">
       <c r="A370">
         <v>369</v>
       </c>
@@ -16532,7 +16543,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" ht="15.75" customHeight="1">
       <c r="A371">
         <v>370</v>
       </c>
@@ -16564,7 +16575,7 @@
         <v/>
       </c>
     </row>
-    <row r="372">
+    <row r="372" ht="15.75" customHeight="1">
       <c r="A372">
         <v>371</v>
       </c>
@@ -16596,7 +16607,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" ht="15.75" customHeight="1">
       <c r="A373">
         <v>372</v>
       </c>
@@ -16628,7 +16639,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" ht="15.75" customHeight="1">
       <c r="A374">
         <v>373</v>
       </c>
@@ -16660,7 +16671,7 @@
         <v/>
       </c>
     </row>
-    <row r="375">
+    <row r="375" ht="15.75" customHeight="1">
       <c r="A375">
         <v>374</v>
       </c>
@@ -16692,7 +16703,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" ht="15.75" customHeight="1">
       <c r="A376">
         <v>375</v>
       </c>
@@ -16724,7 +16735,7 @@
         <v/>
       </c>
     </row>
-    <row r="377">
+    <row r="377" ht="15.75" customHeight="1">
       <c r="A377">
         <v>376</v>
       </c>
@@ -16756,7 +16767,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" ht="15.75" customHeight="1">
       <c r="A378">
         <v>377</v>
       </c>
@@ -16788,7 +16799,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" ht="15.75" customHeight="1">
       <c r="A379">
         <v>378</v>
       </c>
@@ -16820,7 +16831,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="380">
+    <row r="380" ht="15.75" customHeight="1">
       <c r="A380">
         <v>379</v>
       </c>
@@ -16852,7 +16863,7 @@
         <v/>
       </c>
     </row>
-    <row r="381">
+    <row r="381" ht="15.75" customHeight="1">
       <c r="A381">
         <v>380</v>
       </c>
@@ -16884,7 +16895,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" ht="15.75" customHeight="1">
       <c r="A382">
         <v>381</v>
       </c>
@@ -16916,7 +16927,7 @@
         <v/>
       </c>
     </row>
-    <row r="383">
+    <row r="383" ht="15.75" customHeight="1">
       <c r="A383">
         <v>382</v>
       </c>
@@ -16948,7 +16959,7 @@
         <v/>
       </c>
     </row>
-    <row r="384">
+    <row r="384" ht="15.75" customHeight="1">
       <c r="A384">
         <v>383</v>
       </c>
@@ -16980,7 +16991,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" ht="15.75" customHeight="1">
       <c r="A385">
         <v>384</v>
       </c>
@@ -17012,7 +17023,7 @@
         <v/>
       </c>
     </row>
-    <row r="386">
+    <row r="386" ht="15.75" customHeight="1">
       <c r="A386">
         <v>385</v>
       </c>
@@ -17044,7 +17055,7 @@
         <v/>
       </c>
     </row>
-    <row r="387">
+    <row r="387" ht="15.75" customHeight="1">
       <c r="A387">
         <v>386</v>
       </c>
@@ -17076,7 +17087,7 @@
         <v/>
       </c>
     </row>
-    <row r="388">
+    <row r="388" ht="15.75" customHeight="1">
       <c r="A388">
         <v>387</v>
       </c>
@@ -17108,7 +17119,7 @@
         <v/>
       </c>
     </row>
-    <row r="389">
+    <row r="389" ht="15.75" customHeight="1">
       <c r="A389">
         <v>388</v>
       </c>
@@ -17140,7 +17151,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" ht="15.75" customHeight="1">
       <c r="A390">
         <v>389</v>
       </c>
@@ -17172,7 +17183,7 @@
         <v/>
       </c>
     </row>
-    <row r="391">
+    <row r="391" ht="15.75" customHeight="1">
       <c r="A391">
         <v>390</v>
       </c>
@@ -17204,7 +17215,7 @@
         <v/>
       </c>
     </row>
-    <row r="392">
+    <row r="392" ht="15.75" customHeight="1">
       <c r="A392">
         <v>391</v>
       </c>
@@ -17236,7 +17247,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="393">
+    <row r="393" ht="15.75" customHeight="1">
       <c r="A393">
         <v>392</v>
       </c>
@@ -17268,7 +17279,7 @@
         <v/>
       </c>
     </row>
-    <row r="394">
+    <row r="394" ht="15.75" customHeight="1">
       <c r="A394">
         <v>393</v>
       </c>
@@ -17300,7 +17311,7 @@
         <v/>
       </c>
     </row>
-    <row r="395">
+    <row r="395" ht="15.75" customHeight="1">
       <c r="A395">
         <v>394</v>
       </c>
@@ -17332,7 +17343,7 @@
         <v/>
       </c>
     </row>
-    <row r="396">
+    <row r="396" ht="15.75" customHeight="1">
       <c r="A396">
         <v>395</v>
       </c>
@@ -17364,7 +17375,7 @@
         <v/>
       </c>
     </row>
-    <row r="397">
+    <row r="397" ht="15.75" customHeight="1">
       <c r="A397">
         <v>396</v>
       </c>
@@ -17396,7 +17407,7 @@
         <v/>
       </c>
     </row>
-    <row r="398">
+    <row r="398" ht="15.75" customHeight="1">
       <c r="A398">
         <v>397</v>
       </c>
@@ -17428,7 +17439,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" ht="15.75" customHeight="1">
       <c r="A399">
         <v>398</v>
       </c>
@@ -17460,7 +17471,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" ht="15.75" customHeight="1">
       <c r="A400">
         <v>399</v>
       </c>
@@ -17492,7 +17503,7 @@
         <v/>
       </c>
     </row>
-    <row r="401">
+    <row r="401" ht="15.75" customHeight="1">
       <c r="A401">
         <v>400</v>
       </c>
@@ -17524,7 +17535,7 @@
         <v/>
       </c>
     </row>
-    <row r="402">
+    <row r="402" ht="15.75" customHeight="1">
       <c r="A402">
         <v>401</v>
       </c>
@@ -17556,7 +17567,7 @@
         <v/>
       </c>
     </row>
-    <row r="403">
+    <row r="403" ht="15.75" customHeight="1">
       <c r="A403">
         <v>402</v>
       </c>
@@ -17588,7 +17599,7 @@
         <v/>
       </c>
     </row>
-    <row r="404">
+    <row r="404" ht="15.75" customHeight="1">
       <c r="A404">
         <v>403</v>
       </c>
@@ -17620,7 +17631,7 @@
         <v/>
       </c>
     </row>
-    <row r="405">
+    <row r="405" ht="15.75" customHeight="1">
       <c r="A405">
         <v>404</v>
       </c>
@@ -17652,7 +17663,7 @@
         <v/>
       </c>
     </row>
-    <row r="406">
+    <row r="406" ht="15.75" customHeight="1">
       <c r="A406">
         <v>405</v>
       </c>
@@ -17684,7 +17695,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" ht="15.75" customHeight="1">
       <c r="A407">
         <v>406</v>
       </c>
@@ -17716,7 +17727,7 @@
         <v/>
       </c>
     </row>
-    <row r="408">
+    <row r="408" ht="15.75" customHeight="1">
       <c r="A408">
         <v>407</v>
       </c>
@@ -17748,7 +17759,7 @@
         <v/>
       </c>
     </row>
-    <row r="409">
+    <row r="409" ht="15.75" customHeight="1">
       <c r="A409">
         <v>408</v>
       </c>
@@ -17780,7 +17791,7 @@
         <v/>
       </c>
     </row>
-    <row r="410">
+    <row r="410" ht="15.75" customHeight="1">
       <c r="A410">
         <v>409</v>
       </c>
@@ -17812,7 +17823,7 @@
         <v/>
       </c>
     </row>
-    <row r="411">
+    <row r="411" ht="15.75" customHeight="1">
       <c r="A411">
         <v>410</v>
       </c>
@@ -17844,7 +17855,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="412">
+    <row r="412" ht="15.75" customHeight="1">
       <c r="A412">
         <v>411</v>
       </c>
@@ -17876,7 +17887,7 @@
         <v/>
       </c>
     </row>
-    <row r="413">
+    <row r="413" ht="15.75" customHeight="1">
       <c r="A413">
         <v>412</v>
       </c>
@@ -17908,7 +17919,7 @@
         <v/>
       </c>
     </row>
-    <row r="414">
+    <row r="414" ht="15.75" customHeight="1">
       <c r="A414">
         <v>413</v>
       </c>
@@ -17940,7 +17951,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="415">
+    <row r="415" ht="15.75" customHeight="1">
       <c r="A415">
         <v>414</v>
       </c>
@@ -17972,7 +17983,7 @@
         <v/>
       </c>
     </row>
-    <row r="416">
+    <row r="416" ht="15.75" customHeight="1">
       <c r="A416">
         <v>415</v>
       </c>
@@ -18004,7 +18015,7 @@
         <v/>
       </c>
     </row>
-    <row r="417">
+    <row r="417" ht="15.75" customHeight="1">
       <c r="A417">
         <v>416</v>
       </c>
@@ -18036,7 +18047,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" ht="15.75" customHeight="1">
       <c r="A418">
         <v>417</v>
       </c>
@@ -18068,7 +18079,7 @@
         <v/>
       </c>
     </row>
-    <row r="419">
+    <row r="419" ht="15.75" customHeight="1">
       <c r="A419">
         <v>418</v>
       </c>
@@ -18100,7 +18111,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="420">
+    <row r="420" ht="15.75" customHeight="1">
       <c r="A420">
         <v>419</v>
       </c>
@@ -18132,7 +18143,7 @@
         <v/>
       </c>
     </row>
-    <row r="421">
+    <row r="421" ht="15.75" customHeight="1">
       <c r="A421">
         <v>420</v>
       </c>
@@ -18164,7 +18175,7 @@
         <v/>
       </c>
     </row>
-    <row r="422">
+    <row r="422" ht="15.75" customHeight="1">
       <c r="A422">
         <v>421</v>
       </c>
@@ -18196,7 +18207,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="423">
+    <row r="423" ht="15.75" customHeight="1">
       <c r="A423">
         <v>422</v>
       </c>
@@ -18228,7 +18239,7 @@
         <v/>
       </c>
     </row>
-    <row r="424">
+    <row r="424" ht="15.75" customHeight="1">
       <c r="A424">
         <v>423</v>
       </c>
@@ -18260,7 +18271,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="425">
+    <row r="425" ht="15.75" customHeight="1">
       <c r="A425">
         <v>424</v>
       </c>
@@ -18292,7 +18303,7 @@
         <v/>
       </c>
     </row>
-    <row r="426">
+    <row r="426" ht="15.75" customHeight="1">
       <c r="A426">
         <v>425</v>
       </c>
@@ -18324,7 +18335,7 @@
         <v/>
       </c>
     </row>
-    <row r="427">
+    <row r="427" ht="15.75" customHeight="1">
       <c r="A427">
         <v>426</v>
       </c>
@@ -18356,7 +18367,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" ht="15.75" customHeight="1">
       <c r="A428">
         <v>427</v>
       </c>
@@ -18388,7 +18399,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="429">
+    <row r="429" ht="15.75" customHeight="1">
       <c r="A429">
         <v>428</v>
       </c>
@@ -18420,7 +18431,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="430">
+    <row r="430" ht="15.75" customHeight="1">
       <c r="A430">
         <v>429</v>
       </c>
@@ -18452,7 +18463,7 @@
         <v/>
       </c>
     </row>
-    <row r="431">
+    <row r="431" ht="15.75" customHeight="1">
       <c r="A431">
         <v>430</v>
       </c>
@@ -18484,7 +18495,7 @@
         <v/>
       </c>
     </row>
-    <row r="432">
+    <row r="432" ht="15.75" customHeight="1">
       <c r="A432">
         <v>431</v>
       </c>
@@ -18516,7 +18527,7 @@
         <v/>
       </c>
     </row>
-    <row r="433">
+    <row r="433" ht="15.75" customHeight="1">
       <c r="A433">
         <v>432</v>
       </c>
@@ -18548,7 +18559,7 @@
         <v/>
       </c>
     </row>
-    <row r="434">
+    <row r="434" ht="15.75" customHeight="1">
       <c r="A434">
         <v>433</v>
       </c>
@@ -18580,7 +18591,7 @@
         <v/>
       </c>
     </row>
-    <row r="435">
+    <row r="435" ht="15.75" customHeight="1">
       <c r="A435">
         <v>434</v>
       </c>
@@ -18612,7 +18623,7 @@
         <v/>
       </c>
     </row>
-    <row r="436">
+    <row r="436" ht="15.75" customHeight="1">
       <c r="A436">
         <v>435</v>
       </c>
@@ -18644,7 +18655,7 @@
         <v/>
       </c>
     </row>
-    <row r="437">
+    <row r="437" ht="15.75" customHeight="1">
       <c r="A437">
         <v>436</v>
       </c>
@@ -18676,7 +18687,7 @@
         <v/>
       </c>
     </row>
-    <row r="438">
+    <row r="438" ht="15.75" customHeight="1">
       <c r="A438">
         <v>437</v>
       </c>
@@ -18708,7 +18719,7 @@
         <v/>
       </c>
     </row>
-    <row r="439">
+    <row r="439" ht="15.75" customHeight="1">
       <c r="A439">
         <v>438</v>
       </c>
@@ -18740,7 +18751,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" ht="15.75" customHeight="1">
       <c r="A440">
         <v>439</v>
       </c>
@@ -18772,7 +18783,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" ht="15.75" customHeight="1">
       <c r="A441">
         <v>440</v>
       </c>
@@ -18804,7 +18815,7 @@
         <v/>
       </c>
     </row>
-    <row r="442">
+    <row r="442" ht="15.75" customHeight="1">
       <c r="A442">
         <v>441</v>
       </c>
@@ -18836,7 +18847,7 @@
         <v/>
       </c>
     </row>
-    <row r="443">
+    <row r="443" ht="15.75" customHeight="1">
       <c r="A443">
         <v>442</v>
       </c>
@@ -18868,7 +18879,7 @@
         <v/>
       </c>
     </row>
-    <row r="444">
+    <row r="444" ht="15.75" customHeight="1">
       <c r="A444">
         <v>443</v>
       </c>
@@ -18900,7 +18911,7 @@
         <v/>
       </c>
     </row>
-    <row r="445">
+    <row r="445" ht="15.75" customHeight="1">
       <c r="A445">
         <v>444</v>
       </c>
@@ -18932,7 +18943,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" ht="15.75" customHeight="1">
       <c r="A446">
         <v>445</v>
       </c>
@@ -18964,7 +18975,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="447">
+    <row r="447" ht="15.75" customHeight="1">
       <c r="A447">
         <v>446</v>
       </c>
@@ -18996,7 +19007,7 @@
         <v/>
       </c>
     </row>
-    <row r="448">
+    <row r="448" ht="15.75" customHeight="1">
       <c r="A448">
         <v>447</v>
       </c>
@@ -19028,7 +19039,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="449">
+    <row r="449" ht="15.75" customHeight="1">
       <c r="A449">
         <v>448</v>
       </c>
@@ -19060,7 +19071,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" ht="15.75" customHeight="1">
       <c r="A450">
         <v>449</v>
       </c>
@@ -19092,7 +19103,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" ht="15.75" customHeight="1">
       <c r="A451">
         <v>450</v>
       </c>
@@ -19124,7 +19135,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" ht="15.75" customHeight="1">
       <c r="A452">
         <v>451</v>
       </c>
@@ -19156,7 +19167,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" ht="15.75" customHeight="1">
       <c r="A453">
         <v>452</v>
       </c>
@@ -19188,7 +19199,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" ht="15.75" customHeight="1">
       <c r="A454">
         <v>453</v>
       </c>
@@ -19220,7 +19231,7 @@
         <v/>
       </c>
     </row>
-    <row r="455">
+    <row r="455" ht="15.75" customHeight="1">
       <c r="A455">
         <v>454</v>
       </c>
@@ -19252,7 +19263,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" ht="15.75" customHeight="1">
       <c r="A456">
         <v>455</v>
       </c>
@@ -19284,7 +19295,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="457">
+    <row r="457" ht="15.75" customHeight="1">
       <c r="A457">
         <v>456</v>
       </c>
@@ -19316,7 +19327,7 @@
         <v/>
       </c>
     </row>
-    <row r="458">
+    <row r="458" ht="15.75" customHeight="1">
       <c r="A458">
         <v>457</v>
       </c>
@@ -19348,7 +19359,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="459">
+    <row r="459" ht="15.75" customHeight="1">
       <c r="A459">
         <v>458</v>
       </c>
@@ -19380,7 +19391,7 @@
         <v/>
       </c>
     </row>
-    <row r="460">
+    <row r="460" ht="15.75" customHeight="1">
       <c r="A460">
         <v>459</v>
       </c>
@@ -19412,7 +19423,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" ht="15.75" customHeight="1">
       <c r="A461">
         <v>460</v>
       </c>
@@ -19444,7 +19455,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" ht="15.75" customHeight="1">
       <c r="A462">
         <v>461</v>
       </c>
@@ -19476,7 +19487,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" ht="15.75" customHeight="1">
       <c r="A463">
         <v>462</v>
       </c>
@@ -19508,7 +19519,7 @@
         <v/>
       </c>
     </row>
-    <row r="464">
+    <row r="464" ht="15.75" customHeight="1">
       <c r="A464">
         <v>463</v>
       </c>
@@ -19540,7 +19551,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="465">
+    <row r="465" ht="15.75" customHeight="1">
       <c r="A465">
         <v>464</v>
       </c>
@@ -19572,7 +19583,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="466">
+    <row r="466" ht="15.75" customHeight="1">
       <c r="A466">
         <v>465</v>
       </c>
@@ -19604,7 +19615,7 @@
         <v/>
       </c>
     </row>
-    <row r="467">
+    <row r="467" ht="15.75" customHeight="1">
       <c r="A467">
         <v>466</v>
       </c>
@@ -19636,7 +19647,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" ht="15.75" customHeight="1">
       <c r="A468">
         <v>467</v>
       </c>
@@ -19668,7 +19679,7 @@
         <v/>
       </c>
     </row>
-    <row r="469">
+    <row r="469" ht="15.75" customHeight="1">
       <c r="A469">
         <v>468</v>
       </c>
@@ -19700,7 +19711,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" ht="15.75" customHeight="1">
       <c r="A470">
         <v>469</v>
       </c>
@@ -19732,7 +19743,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" ht="15.75" customHeight="1">
       <c r="A471">
         <v>470</v>
       </c>
@@ -19764,7 +19775,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="472">
+    <row r="472" ht="15.75" customHeight="1">
       <c r="A472">
         <v>471</v>
       </c>
@@ -19796,7 +19807,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="473">
+    <row r="473" ht="15.75" customHeight="1">
       <c r="A473">
         <v>472</v>
       </c>
@@ -19828,7 +19839,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" ht="15.75" customHeight="1">
       <c r="A474">
         <v>473</v>
       </c>
@@ -19860,7 +19871,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="475">
+    <row r="475" ht="15.75" customHeight="1">
       <c r="A475">
         <v>474</v>
       </c>
@@ -19892,7 +19903,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" ht="15.75" customHeight="1">
       <c r="A476">
         <v>475</v>
       </c>
@@ -19924,7 +19935,7 @@
         <v/>
       </c>
     </row>
-    <row r="477">
+    <row r="477" ht="15.75" customHeight="1">
       <c r="A477">
         <v>476</v>
       </c>
@@ -19956,7 +19967,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" ht="15.75" customHeight="1">
       <c r="A478">
         <v>477</v>
       </c>
@@ -19988,7 +19999,7 @@
         <v/>
       </c>
     </row>
-    <row r="479">
+    <row r="479" ht="15.75" customHeight="1">
       <c r="A479">
         <v>478</v>
       </c>
@@ -20020,7 +20031,7 @@
         <v/>
       </c>
     </row>
-    <row r="480">
+    <row r="480" ht="15.75" customHeight="1">
       <c r="A480">
         <v>479</v>
       </c>
@@ -20052,7 +20063,7 @@
         <v/>
       </c>
     </row>
-    <row r="481">
+    <row r="481" ht="15.75" customHeight="1">
       <c r="A481">
         <v>480</v>
       </c>
@@ -20084,7 +20095,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" ht="15.75" customHeight="1">
       <c r="A482">
         <v>481</v>
       </c>
@@ -20116,7 +20127,7 @@
         <v/>
       </c>
     </row>
-    <row r="483">
+    <row r="483" ht="15.75" customHeight="1">
       <c r="A483">
         <v>482</v>
       </c>
@@ -20148,7 +20159,7 @@
         <v/>
       </c>
     </row>
-    <row r="484">
+    <row r="484" ht="15.75" customHeight="1">
       <c r="A484">
         <v>483</v>
       </c>
@@ -20180,7 +20191,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="485">
+    <row r="485" ht="15.75" customHeight="1">
       <c r="A485">
         <v>484</v>
       </c>
@@ -20212,7 +20223,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="486">
+    <row r="486" ht="15.75" customHeight="1">
       <c r="A486">
         <v>485</v>
       </c>
@@ -20244,7 +20255,7 @@
         <v/>
       </c>
     </row>
-    <row r="487">
+    <row r="487" ht="15.75" customHeight="1">
       <c r="A487">
         <v>486</v>
       </c>
@@ -20276,7 +20287,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="488">
+    <row r="488" ht="15.75" customHeight="1">
       <c r="A488">
         <v>487</v>
       </c>
@@ -20308,7 +20319,7 @@
         <v>2026-08-06</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" ht="15.75" customHeight="1">
       <c r="A489">
         <v>488</v>
       </c>
@@ -20352,7 +20363,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C19"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="str">
         <v>Staging Environment</v>
       </c>
@@ -20363,7 +20374,7 @@
         <v>Staging Environment</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="str">
         <v>https://stg.quantarra.com/</v>
       </c>
@@ -20374,7 +20385,7 @@
         <v>Audit: https://audit-stg.quantarra.com/</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" t="str">
         <v>Role</v>
       </c>
@@ -20385,7 +20396,7 @@
         <v>Password</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" t="str">
         <v>Super user</v>
       </c>
@@ -20396,7 +20407,7 @@
         <v>Quantarra2026!</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" t="str">
         <v>Administrator</v>
       </c>
@@ -20407,7 +20418,7 @@
         <v>Quantarra2026!</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" t="str">
         <v>Contributor</v>
       </c>
@@ -20418,7 +20429,7 @@
         <v>Quantarra2026!</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" t="str">
         <v>Viewer</v>
       </c>
@@ -20429,7 +20440,7 @@
         <v>Quantarra2026!</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" t="str">
         <v>POC Environment</v>
       </c>
@@ -20440,7 +20451,7 @@
         <v>POC Environment</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" t="str">
         <v>https://poc.quantarra.com/</v>
       </c>
@@ -20451,7 +20462,7 @@
         <v>Audit: https://audit-poc.quantarra.com/</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" t="str">
         <v>Role</v>
       </c>
@@ -20462,7 +20473,7 @@
         <v>Password</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" t="str">
         <v>Admin</v>
       </c>
@@ -20473,7 +20484,7 @@
         <v>Quantarra2026!</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" t="str">
         <v>Contributor</v>
       </c>
@@ -20484,7 +20495,7 @@
         <v>Quantarra2026!</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" t="str">
         <v>Prod Environment</v>
       </c>
@@ -20495,7 +20506,7 @@
         <v>Prod Environment</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" t="str">
         <v>https://app.quantarra.com/</v>
       </c>
@@ -20506,7 +20517,7 @@
         <v>{"text":"Audit: Not ready","hyperlink":""}</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" t="str">
         <v>Role</v>
       </c>
@@ -20517,7 +20528,7 @@
         <v>Password</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" t="str">
         <v>Admin / Super User</v>
       </c>
@@ -20528,7 +20539,7 @@
         <v>Quantarra2026!</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" t="str">
         <v>Contributor</v>
       </c>
@@ -20568,7 +20579,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="str">
         <v>Jira Key</v>
       </c>
@@ -20603,7 +20614,7 @@
         <v>Environment</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="str">
         <v>PRJAT-880</v>
       </c>
@@ -20638,7 +20649,7 @@
         <v>Staging</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" t="str">
         <v>PRJAT-887</v>
       </c>
@@ -20673,7 +20684,7 @@
         <v>Staging</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" t="str">
         <v/>
       </c>
@@ -20708,7 +20719,7 @@
         <v>Staging</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" t="str">
         <v>PRJAT-1260</v>
       </c>
@@ -20755,7 +20766,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C10"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="str">
         <v>Setting</v>
       </c>
@@ -20766,7 +20777,7 @@
         <v>Description</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="str">
         <v>Slack Notifications</v>
       </c>
@@ -20777,7 +20788,7 @@
         <v>Post to Slack channel on test failures (Yes/No)</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" t="str">
         <v>Email Notifications</v>
       </c>
@@ -20788,7 +20799,7 @@
         <v>Send email report after every run (Yes/No)</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" t="str">
         <v>Jira Ticket Creation</v>
       </c>
@@ -20799,7 +20810,7 @@
         <v>Create/update Jira tickets on failures (Yes/No)</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" t="str">
         <v>Report Environment</v>
       </c>
@@ -20810,7 +20821,7 @@
         <v>Which environment(s) to report: prod / poc / both</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" t="str">
         <v>Email Recipients</v>
       </c>
@@ -20818,7 +20829,7 @@
         <v>keerthi@quantarra.io</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" t="str">
         <v>Notes:</v>
       </c>
@@ -20829,7 +20840,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" t="str">
         <v>• Change "Value" column to Yes/No to toggle features.</v>
       </c>
@@ -20840,7 +20851,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" t="str">
         <v>• Changes take effect on the next shakeout run (no deploy needed).</v>
       </c>
@@ -20851,7 +20862,7 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" t="str">
         <v>• Push to GitHub for CI runs to pick up changes.</v>
       </c>
